--- a/Projeto/Projeto-modelo.xlsx
+++ b/Projeto/Projeto-modelo.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="387">
   <si>
     <t xml:space="preserve">Projeto e desenvolvimento — Como usar esta planilha</t>
   </si>
@@ -549,7 +549,7 @@
     <t xml:space="preserve">Fichas técnicas comparadas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Queda de dardo repetida: 410 g.</t>
+    <t xml:space="preserve">Queda de dardo no lote de teste: 420 g.</t>
   </si>
   <si>
     <t xml:space="preserve">Gerente de engenharia</t>
@@ -714,7 +714,7 @@
     <t xml:space="preserve">Observações</t>
   </si>
   <si>
-    <t xml:space="preserve">Está decidido se a organização faz projeto e desenvolvimento, e a exclusão, se houver, está justificada.</t>
+    <t xml:space="preserve">Está decidido se a organização faz projeto e desenvolvimento, e a não aplicabilidade, se houver, está justificada.</t>
   </si>
   <si>
     <t xml:space="preserve">Cada projeto tem um plano: etapas, responsáveis, prazos, análises críticas, verificações e validações.</t>
@@ -897,7 +897,7 @@
     <t xml:space="preserve">Conferência da ficha técnica e dos rótulos dos insumos</t>
   </si>
   <si>
-    <t xml:space="preserve">Rótulos conferidos em 20/04.</t>
+    <t xml:space="preserve">Rótulos conferidos em 20/04. Vale para a receita verificada até 03/05: com o queijo da marca B (12/05) e o tofu defumado (18/05), a ficha técnica e os rótulos precisam ser conferidos de novo.</t>
   </si>
   <si>
     <t xml:space="preserve">E2</t>
@@ -915,21 +915,24 @@
     <t xml:space="preserve">Conferência do texto contra a ficha técnica</t>
   </si>
   <si>
+    <t xml:space="preserve">Texto conferido em 03/05. Vale para a receita verificada até 03/05: com o queijo da marca B (12/05) e o tofu defumado (18/05), o texto de alergênicos precisa ser conferido de novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aviso de que a cozinha é compartilhada com produtos de origem animal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oferta: o que a loja não garante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texto do cardápio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conferência do texto</t>
+  </si>
+  <si>
     <t xml:space="preserve">Texto conferido em 03/05.</t>
   </si>
   <si>
-    <t xml:space="preserve">Aviso de que a cozinha é compartilhada com produtos de origem animal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oferta: o que a loja não garante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texto do cardápio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conferência do texto</t>
-  </si>
-  <si>
     <t xml:space="preserve">E4</t>
   </si>
   <si>
@@ -1182,7 +1185,7 @@
     <t xml:space="preserve">Laudo de migração de laboratório externo</t>
   </si>
   <si>
-    <t xml:space="preserve">Laudo de 12/07.</t>
+    <t xml:space="preserve">Laudo de 18/07.</t>
   </si>
   <si>
     <t xml:space="preserve">Método de ensaio de queda de dardo da norma técnica.</t>
@@ -1263,7 +1266,7 @@
     <t xml:space="preserve">Fichas técnicas comparadas. Laudo de migração estendido à resina B.</t>
   </si>
   <si>
-    <t xml:space="preserve">Queda de dardo repetida com a resina B: 410 g, conforme.</t>
+    <t xml:space="preserve">Queda de dardo no lote de teste, com a resina B: 420 g, em 16/07, conforme.</t>
   </si>
   <si>
     <t xml:space="preserve">Camada interna de 15 para 20 µm.</t>
@@ -2103,11 +2106,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="54331943"/>
-        <c:axId val="96305777"/>
+        <c:axId val="19066209"/>
+        <c:axId val="32375924"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="54331943"/>
+        <c:axId val="19066209"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2139,7 +2142,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96305777"/>
+        <c:crossAx val="32375924"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2147,7 +2150,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="96305777"/>
+        <c:axId val="32375924"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2187,7 +2190,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54331943"/>
+        <c:crossAx val="19066209"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -4412,7 +4415,7 @@
         <v>112</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>46588</v>
+        <v>46576</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>137</v>
@@ -6269,7 +6272,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="32" t="s">
         <v>251</v>
       </c>
@@ -6359,7 +6362,7 @@
         <v>119</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -6370,29 +6373,29 @@
     </row>
     <row r="28" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D28" s="28"/>
       <c r="E28" s="29" t="s">
         <v>115</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I28" s="29" t="s">
         <v>119</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -6403,29 +6406,29 @@
     </row>
     <row r="29" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="32" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D29" s="28"/>
       <c r="E29" s="29" t="s">
         <v>115</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I29" s="29" t="s">
         <v>119</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -6436,29 +6439,29 @@
     </row>
     <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="32" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D30" s="28"/>
       <c r="E30" s="29" t="s">
         <v>189</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I30" s="29" t="s">
         <v>22</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -6469,29 +6472,29 @@
     </row>
     <row r="31" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="32" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D31" s="28"/>
       <c r="E31" s="29" t="s">
         <v>187</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I31" s="29" t="s">
         <v>119</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -6502,23 +6505,23 @@
     </row>
     <row r="32" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="32" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D32" s="28"/>
       <c r="E32" s="29" t="s">
         <v>189</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I32" s="29"/>
       <c r="J32" s="7"/>
@@ -6562,7 +6565,7 @@
       </c>
       <c r="H35" s="27"/>
       <c r="I35" s="27" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J35" s="27"/>
       <c r="K35" s="27"/>
@@ -6578,11 +6581,11 @@
         <v>46519</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D36" s="28"/>
       <c r="E36" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
@@ -6603,15 +6606,15 @@
         <v>46525</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D37" s="28"/>
       <c r="E37" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
@@ -6643,7 +6646,7 @@
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
@@ -6681,7 +6684,7 @@
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
@@ -6948,7 +6951,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="24" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E4" s="24"/>
       <c r="F4" s="24"/>
@@ -6966,7 +6969,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="24" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="24"/>
@@ -6984,7 +6987,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="24" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="24"/>
@@ -7002,7 +7005,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="24" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="24"/>
@@ -7020,7 +7023,7 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="24" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="24"/>
@@ -7038,7 +7041,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="24" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="24"/>
@@ -7056,7 +7059,7 @@
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E10" s="24"/>
       <c r="F10" s="24"/>
@@ -7134,7 +7137,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D15" s="28"/>
       <c r="E15" s="29" t="s">
@@ -7144,7 +7147,7 @@
         <v>141</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H15" s="30" t="n">
         <v>46549</v>
@@ -7157,7 +7160,7 @@
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M15" s="14" t="str">
         <f aca="false">IF(C15="",IF(1&gt;0,"Falta a etapa",""),IF(E15="","Falta o tipo",IF(F15="","Falta o responsável",IF(H15="","Falta o prazo",IF(AND(I15&lt;&gt;"",J15=""),"Falta o resultado",IF(AND(J15&lt;&gt;"",I15=""),"Falta a data de conclusão",IF(AND(OR(J15="Aprovado com ressalvas",J15="Reprovado"),K15=""),"Falta a ação",IF(AND(E15="Liberação para produção",I15&lt;&gt;"",COUNTIFS($E$15:$E$23,"Validação",$J$15:$J$23,"Aprovado")+COUNTIFS($E$15:$E$23,"Validação",$J$15:$J$23,"Aprovado com ressalvas")=0),"Liberado sem validação aprovada",IF(AND(I15="",ISNUMBER($D$11),H15&lt;$D$11),"Atrasada","OK")))))))))</f>
@@ -7169,7 +7172,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D16" s="28"/>
       <c r="E16" s="29" t="s">
@@ -7179,7 +7182,7 @@
         <v>141</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H16" s="30" t="n">
         <v>46563</v>
@@ -7192,7 +7195,7 @@
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M16" s="14" t="str">
         <f aca="false">IF(C16="",IF(1&gt;0,"Falta a etapa",""),IF(E16="","Falta o tipo",IF(F16="","Falta o responsável",IF(H16="","Falta o prazo",IF(AND(I16&lt;&gt;"",J16=""),"Falta o resultado",IF(AND(J16&lt;&gt;"",I16=""),"Falta a data de conclusão",IF(AND(OR(J16="Aprovado com ressalvas",J16="Reprovado"),K16=""),"Falta a ação",IF(AND(E16="Liberação para produção",I16&lt;&gt;"",COUNTIFS($E$15:$E$23,"Validação",$J$15:$J$23,"Aprovado")+COUNTIFS($E$15:$E$23,"Validação",$J$15:$J$23,"Aprovado com ressalvas")=0),"Liberado sem validação aprovada",IF(AND(I16="",ISNUMBER($D$11),H16&lt;$D$11),"Atrasada","OK")))))))))</f>
@@ -7204,7 +7207,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D17" s="28"/>
       <c r="E17" s="29" t="s">
@@ -7214,7 +7217,7 @@
         <v>141</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H17" s="30" t="n">
         <v>46566</v>
@@ -7227,7 +7230,7 @@
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M17" s="14" t="str">
         <f aca="false">IF(C17="",IF(1&gt;0,"Falta a etapa",""),IF(E17="","Falta o tipo",IF(F17="","Falta o responsável",IF(H17="","Falta o prazo",IF(AND(I17&lt;&gt;"",J17=""),"Falta o resultado",IF(AND(J17&lt;&gt;"",I17=""),"Falta a data de conclusão",IF(AND(OR(J17="Aprovado com ressalvas",J17="Reprovado"),K17=""),"Falta a ação",IF(AND(E17="Liberação para produção",I17&lt;&gt;"",COUNTIFS($E$15:$E$23,"Validação",$J$15:$J$23,"Aprovado")+COUNTIFS($E$15:$E$23,"Validação",$J$15:$J$23,"Aprovado com ressalvas")=0),"Liberado sem validação aprovada",IF(AND(I17="",ISNUMBER($D$11),H17&lt;$D$11),"Atrasada","OK")))))))))</f>
@@ -7239,17 +7242,17 @@
         <v>4</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="29" t="s">
         <v>175</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H18" s="30" t="n">
         <v>46584</v>
@@ -7261,10 +7264,10 @@
         <v>237</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M18" s="14" t="str">
         <f aca="false">IF(C18="",IF(1&gt;0,"Falta a etapa",""),IF(E18="","Falta o tipo",IF(F18="","Falta o responsável",IF(H18="","Falta o prazo",IF(AND(I18&lt;&gt;"",J18=""),"Falta o resultado",IF(AND(J18&lt;&gt;"",I18=""),"Falta a data de conclusão",IF(AND(OR(J18="Aprovado com ressalvas",J18="Reprovado"),K18=""),"Falta a ação",IF(AND(E18="Liberação para produção",I18&lt;&gt;"",COUNTIFS($E$15:$E$23,"Validação",$J$15:$J$23,"Aprovado")+COUNTIFS($E$15:$E$23,"Validação",$J$15:$J$23,"Aprovado com ressalvas")=0),"Liberado sem validação aprovada",IF(AND(I18="",ISNUMBER($D$11),H18&lt;$D$11),"Atrasada","OK")))))))))</f>
@@ -7276,7 +7279,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D19" s="28"/>
       <c r="E19" s="29" t="s">
@@ -7286,7 +7289,7 @@
         <v>141</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H19" s="30" t="n">
         <v>46605</v>
@@ -7295,13 +7298,13 @@
         <v>46608</v>
       </c>
       <c r="J19" s="29" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M19" s="14" t="str">
         <f aca="false">IF(C19="",IF(1&gt;0,"Falta a etapa",""),IF(E19="","Falta o tipo",IF(F19="","Falta o responsável",IF(H19="","Falta o prazo",IF(AND(I19&lt;&gt;"",J19=""),"Falta o resultado",IF(AND(J19&lt;&gt;"",I19=""),"Falta a data de conclusão",IF(AND(OR(J19="Aprovado com ressalvas",J19="Reprovado"),K19=""),"Falta a ação",IF(AND(E19="Liberação para produção",I19&lt;&gt;"",COUNTIFS($E$15:$E$23,"Validação",$J$15:$J$23,"Aprovado")+COUNTIFS($E$15:$E$23,"Validação",$J$15:$J$23,"Aprovado com ressalvas")=0),"Liberado sem validação aprovada",IF(AND(I19="",ISNUMBER($D$11),H19&lt;$D$11),"Atrasada","OK")))))))))</f>
@@ -7313,7 +7316,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D20" s="28"/>
       <c r="E20" s="29" t="s">
@@ -7323,7 +7326,7 @@
         <v>141</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H20" s="30" t="n">
         <v>46612</v>
@@ -7336,7 +7339,7 @@
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M20" s="14" t="str">
         <f aca="false">IF(C20="",IF(1&gt;0,"Falta a etapa",""),IF(E20="","Falta o tipo",IF(F20="","Falta o responsável",IF(H20="","Falta o prazo",IF(AND(I20&lt;&gt;"",J20=""),"Falta o resultado",IF(AND(J20&lt;&gt;"",I20=""),"Falta a data de conclusão",IF(AND(OR(J20="Aprovado com ressalvas",J20="Reprovado"),K20=""),"Falta a ação",IF(AND(E20="Liberação para produção",I20&lt;&gt;"",COUNTIFS($E$15:$E$23,"Validação",$J$15:$J$23,"Aprovado")+COUNTIFS($E$15:$E$23,"Validação",$J$15:$J$23,"Aprovado com ressalvas")=0),"Liberado sem validação aprovada",IF(AND(I20="",ISNUMBER($D$11),H20&lt;$D$11),"Atrasada","OK")))))))))</f>
@@ -7348,17 +7351,17 @@
         <v>7</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D21" s="28"/>
       <c r="E21" s="29" t="s">
         <v>175</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H21" s="30" t="n">
         <v>46626</v>
@@ -7377,7 +7380,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D22" s="28"/>
       <c r="E22" s="29" t="s">
@@ -7387,7 +7390,7 @@
         <v>141</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H22" s="30" t="n">
         <v>46647</v>
@@ -7406,7 +7409,7 @@
         <v>9</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D23" s="28"/>
       <c r="E23" s="29" t="s">
@@ -7416,7 +7419,7 @@
         <v>141</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H23" s="30" t="n">
         <v>46654</v>
@@ -7483,26 +7486,26 @@
         <v>251</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D27" s="28"/>
       <c r="E27" s="29" t="s">
         <v>184</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I27" s="29" t="s">
         <v>119</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -7516,26 +7519,26 @@
         <v>257</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D28" s="28"/>
       <c r="E28" s="29" t="s">
         <v>184</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I28" s="29" t="s">
         <v>119</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -7559,7 +7562,7 @@
         <v>116</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>118</v>
@@ -7579,29 +7582,29 @@
     </row>
     <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D30" s="28"/>
       <c r="E30" s="29" t="s">
         <v>185</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I30" s="29" t="s">
         <v>119</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -7612,29 +7615,29 @@
     </row>
     <row r="31" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="32" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D31" s="28"/>
       <c r="E31" s="29" t="s">
         <v>186</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I31" s="29" t="s">
         <v>119</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -7645,29 +7648,29 @@
     </row>
     <row r="32" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="32" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D32" s="28"/>
       <c r="E32" s="29" t="s">
         <v>187</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I32" s="29" t="s">
         <v>119</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -7678,29 +7681,29 @@
     </row>
     <row r="33" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="32" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D33" s="28"/>
       <c r="E33" s="29" t="s">
         <v>184</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I33" s="29" t="s">
         <v>119</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -7711,29 +7714,29 @@
     </row>
     <row r="34" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="32" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D34" s="28"/>
       <c r="E34" s="29" t="s">
         <v>189</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I34" s="29" t="s">
         <v>22</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -7744,23 +7747,23 @@
     </row>
     <row r="35" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="32" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D35" s="28"/>
       <c r="E35" s="29" t="s">
         <v>188</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I35" s="29"/>
       <c r="J35" s="7"/>
@@ -7804,7 +7807,7 @@
       </c>
       <c r="H38" s="27"/>
       <c r="I38" s="27" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J38" s="27"/>
       <c r="K38" s="27"/>
@@ -7817,22 +7820,22 @@
     </row>
     <row r="39" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="34" t="n">
-        <v>46588</v>
+        <v>46576</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D39" s="28"/>
       <c r="E39" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
@@ -7849,19 +7852,19 @@
         <v>46611</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D40" s="28"/>
       <c r="E40" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
@@ -7878,11 +7881,11 @@
         <v>46621</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D41" s="28"/>
       <c r="E41" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
@@ -7891,7 +7894,7 @@
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
       <c r="L41" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M41" s="14" t="str">
         <f aca="false">IF(C41="",IF(1&gt;0,"Falta o que mudou",""),IF(G41="","Falta a análise",IF(L41="","Falta quem autorizou",IF(I41="","Falta o que foi verificado de novo","OK"))))</f>
@@ -7916,7 +7919,7 @@
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
@@ -7954,7 +7957,7 @@
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>

--- a/Projeto/Projeto-modelo.xlsx
+++ b/Projeto/Projeto-modelo.xlsx
@@ -2106,11 +2106,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="19066209"/>
-        <c:axId val="32375924"/>
+        <c:axId val="75740407"/>
+        <c:axId val="18636437"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="19066209"/>
+        <c:axId val="75740407"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2142,7 +2142,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32375924"/>
+        <c:crossAx val="18636437"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2150,7 +2150,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="32375924"/>
+        <c:axId val="18636437"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2190,7 +2190,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19066209"/>
+        <c:crossAx val="75740407"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
